--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/MyData/Sunbeam/2026/Feb/DMC/ios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01571B28-A800-0D4B-92CD-6310B9C7338D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E524F5A5-10BC-E14C-906F-2E0568CFDAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20160" xr2:uid="{37036CD4-DDA0-9D48-BE68-D86624B894EC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Project template</t>
   </si>
@@ -121,6 +121,24 @@
   </si>
   <si>
     <t>emulator (qemu), genymotion, bluestack</t>
+  </si>
+  <si>
+    <t>application</t>
+  </si>
+  <si>
+    <t>android.app.Application</t>
+  </si>
+  <si>
+    <t>UIApplication</t>
+  </si>
+  <si>
+    <t>screen</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>UIViewController</t>
   </si>
 </sst>
 </file>
@@ -492,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704EA995-E638-FA46-BF5A-4CB19ED74678}">
-  <dimension ref="B1:E8"/>
+  <dimension ref="B1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -566,6 +584,28 @@
       </c>
       <c r="E8" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
